--- a/Result/profitability/1236.xlsx
+++ b/Result/profitability/1236.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05125000000000002</v>
+        <v>0.003750000000000017</v>
       </c>
       <c r="N2" t="n">
-        <v>26.3925</v>
+        <v>25.395</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04000000000000002</v>
+        <v>-0.001249999999999984</v>
       </c>
       <c r="N3" t="n">
-        <v>26.09375</v>
+        <v>24.75625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>0.13125</v>
+        <v>0.07500000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>26.89125</v>
+        <v>25.52</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.165</v>
+        <v>0.18875</v>
       </c>
       <c r="N5" t="n">
-        <v>27.40125</v>
+        <v>27.42</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.31625</v>
+        <v>0.23125</v>
       </c>
       <c r="N6" t="n">
-        <v>29.25</v>
+        <v>27.87875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.27625</v>
+        <v>0.2525000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>29.43875</v>
+        <v>28.4975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3675</v>
+        <v>0.29</v>
       </c>
       <c r="N8" t="n">
-        <v>30.88875</v>
+        <v>29.5325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>340</v>
+      </c>
+      <c r="D75" t="n">
+        <v>281</v>
+      </c>
+      <c r="E75" t="n">
+        <v>59</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-57</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-51</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08249999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.59625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.695652173913043</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3862584549661802</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3275862068965516</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1499999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.008777062609713226</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
